--- a/test/fixtures/mikcb_course_import_template.xlsx
+++ b/test/fixtures/mikcb_course_import_template.xlsx
@@ -1,34 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <definedNames/>
+  <calcPr calcId="122211" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,13 +48,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -343,9 +411,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -353,21 +425,6 @@
           <t># mikcb-course-import-v1</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
-      <c r="K1" t="inlineStr"/>
-      <c r="L1" t="inlineStr"/>
-      <c r="M1" t="inlineStr"/>
-      <c r="N1" t="inlineStr"/>
-      <c r="O1" t="inlineStr"/>
-      <c r="P1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -454,7 +511,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>概率论与数理统计</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -464,22 +521,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1-16</t>
+          <t>1-14</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>高数</t>
+          <t>概率论</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -489,213 +546,323 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>A101</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>#2196F3</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+          <t>教学楼A-301</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>必修</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>微积分基础</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>大学英语</t>
+          <t>数字电子技术(B)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1-8、10-16</t>
+          <t>1-16</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t/>
+          <t>数电</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>李老师</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>教学楼201</t>
+          <t>教学楼B-205</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t/>
+          <t>14:00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t/>
+          <t>15:40</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+          <t>4CAF50</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>选修</t>
+          <t>必修</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>口语强化</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+          <t>数字电路基础</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>程序设计</t>
+          <t>数据结构</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1-16</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>数据结构</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>王老师</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>教学楼A-207</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>必修</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>毛泽东思想和中国特色社会主义理论体系概论</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1-14</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>毛概</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>赵老师</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>教学楼A-105</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>#2196F3</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>必修</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>数据结构(实验)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>1-5、7-11单</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>程设</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>李老师</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>实验室</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>4CAF50</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>数据结构实验</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>王老师</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>实验楼S-205</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>必修</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Python入门</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>实验课需自带电脑</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>上机实验</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>大学物理B(2)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1-10(双)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>大学物理</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>孙老师</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>教学楼C-102</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>必修</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -703,18 +870,26 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
